--- a/ig/publication-101/all-profiles.xlsx
+++ b/ig/publication-101/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1-ballot</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T08:49:00+00:00</t>
+    <t>2024-03-29T09:04:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/publication-101/all-profiles.xlsx
+++ b/ig/publication-101/all-profiles.xlsx
@@ -54,7 +54,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T09:04:17+00:00</t>
+    <t>2024-03-29T13:25:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
